--- a/data/final/comexstat/base_comexstat_total_mensal_larga.xlsx
+++ b/data/final/comexstat/base_comexstat_total_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX81"/>
+  <dimension ref="A1:AX82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10877,34 +10877,34 @@
         <v>46053</v>
       </c>
       <c r="B74" t="n">
-        <v>24576605744</v>
+        <v>24573982812</v>
       </c>
       <c r="C74" t="n">
-        <v>20831691725</v>
+        <v>20804455231</v>
       </c>
       <c r="D74" t="n">
-        <v>3744914019</v>
+        <v>3769527581</v>
       </c>
       <c r="E74" t="n">
-        <v>45408297469</v>
+        <v>45378438043</v>
       </c>
       <c r="F74" t="n">
-        <v>59812186143</v>
+        <v>59760718624</v>
       </c>
       <c r="G74" t="n">
-        <v>14315306356</v>
+        <v>14315300646</v>
       </c>
       <c r="H74" t="n">
-        <v>946935529</v>
+        <v>946779078</v>
       </c>
       <c r="I74" t="n">
-        <v>19491349</v>
+        <v>19474260</v>
       </c>
       <c r="J74" t="n">
-        <v>21798118603</v>
+        <v>21770708569</v>
       </c>
       <c r="K74" t="n">
-        <v>619967622</v>
+        <v>621313185</v>
       </c>
       <c r="L74" t="n">
         <v>1693480220</v>
@@ -10916,7 +10916,7 @@
         <v>61236</v>
       </c>
       <c r="O74" t="n">
-        <v>1013528628</v>
+        <v>1013537659</v>
       </c>
       <c r="P74" t="n">
         <v>141224032</v>
@@ -10960,10 +10960,10 @@
         <v>6000000</v>
       </c>
       <c r="AE74" t="n">
-        <v>925674649</v>
+        <v>913562892</v>
       </c>
       <c r="AF74" t="n">
-        <v>4245185990</v>
+        <v>4193768101</v>
       </c>
       <c r="AG74" t="n">
         <v>19110389</v>
@@ -10972,7 +10972,7 @@
         <v>116981840</v>
       </c>
       <c r="AI74" t="n">
-        <v>1843157505</v>
+        <v>1843476386</v>
       </c>
       <c r="AJ74" t="n">
         <v>26379004618</v>
@@ -11021,34 +11021,34 @@
         <v>46081</v>
       </c>
       <c r="B75" t="n">
-        <v>26276065434</v>
+        <v>26270542130</v>
       </c>
       <c r="C75" t="n">
-        <v>22215553623</v>
+        <v>22218059385</v>
       </c>
       <c r="D75" t="n">
-        <v>4060511811</v>
+        <v>4052482745</v>
       </c>
       <c r="E75" t="n">
-        <v>48491619057</v>
+        <v>48488601515</v>
       </c>
       <c r="F75" t="n">
-        <v>61246580653</v>
+        <v>61246448586</v>
       </c>
       <c r="G75" t="n">
-        <v>13059952654</v>
+        <v>13059878341</v>
       </c>
       <c r="H75" t="n">
-        <v>887917741</v>
+        <v>887917882</v>
       </c>
       <c r="I75" t="n">
-        <v>21747059</v>
+        <v>21747055</v>
       </c>
       <c r="J75" t="n">
-        <v>23125218423</v>
+        <v>23127724322</v>
       </c>
       <c r="K75" t="n">
-        <v>713726654</v>
+        <v>717030066</v>
       </c>
       <c r="L75" t="n">
         <v>1982573452</v>
@@ -11120,7 +11120,7 @@
         <v>34072660</v>
       </c>
       <c r="AI75" t="n">
-        <v>1840522680</v>
+        <v>1833120931</v>
       </c>
       <c r="AJ75" t="n">
         <v>26187389970</v>
@@ -11152,7 +11152,7 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr"/>
       <c r="AU75" t="n">
-        <v>2897179100</v>
+        <v>2897179101</v>
       </c>
       <c r="AV75" t="n">
         <v>7101012525</v>
@@ -11169,34 +11169,34 @@
         <v>46112</v>
       </c>
       <c r="B76" t="n">
-        <v>31767869262</v>
+        <v>31766018083</v>
       </c>
       <c r="C76" t="n">
-        <v>25308911941</v>
+        <v>25309170318</v>
       </c>
       <c r="D76" t="n">
-        <v>6458957321</v>
+        <v>6456847765</v>
       </c>
       <c r="E76" t="n">
-        <v>57076781203</v>
+        <v>57075188401</v>
       </c>
       <c r="F76" t="n">
-        <v>69086532981</v>
+        <v>69086215319</v>
       </c>
       <c r="G76" t="n">
-        <v>15883329662</v>
+        <v>15883566500</v>
       </c>
       <c r="H76" t="n">
-        <v>1095660149</v>
+        <v>1095622190</v>
       </c>
       <c r="I76" t="n">
-        <v>30697751</v>
+        <v>30697718</v>
       </c>
       <c r="J76" t="n">
-        <v>26435269841</v>
+        <v>26435490226</v>
       </c>
       <c r="K76" t="n">
-        <v>543861591</v>
+        <v>545703069</v>
       </c>
       <c r="L76" t="n">
         <v>1551914338</v>
@@ -11264,7 +11264,7 @@
         <v>103043600</v>
       </c>
       <c r="AI76" t="n">
-        <v>1779291584</v>
+        <v>1774813115</v>
       </c>
       <c r="AJ76" t="n">
         <v>25768212538</v>
@@ -11313,34 +11313,34 @@
         <v>46142</v>
       </c>
       <c r="B77" t="n">
-        <v>34303112660</v>
+        <v>34286658184</v>
       </c>
       <c r="C77" t="n">
-        <v>23647082379</v>
+        <v>23650669724</v>
       </c>
       <c r="D77" t="n">
-        <v>10656030281</v>
+        <v>10635988460</v>
       </c>
       <c r="E77" t="n">
-        <v>57950195039</v>
+        <v>57937327908</v>
       </c>
       <c r="F77" t="n">
-        <v>75020929456</v>
+        <v>75020841917</v>
       </c>
       <c r="G77" t="n">
-        <v>14068303977</v>
+        <v>14068462213</v>
       </c>
       <c r="H77" t="n">
-        <v>1093353315</v>
+        <v>1093376528</v>
       </c>
       <c r="I77" t="n">
-        <v>26781461</v>
+        <v>26781417</v>
       </c>
       <c r="J77" t="n">
-        <v>24767217155</v>
+        <v>24770827669</v>
       </c>
       <c r="K77" t="n">
-        <v>344673367</v>
+        <v>346153809</v>
       </c>
       <c r="L77" t="n">
         <v>958119849</v>
@@ -11352,7 +11352,7 @@
         <v>81647</v>
       </c>
       <c r="O77" t="n">
-        <v>1072315176</v>
+        <v>1072316499</v>
       </c>
       <c r="P77" t="n">
         <v>171392428</v>
@@ -11408,7 +11408,7 @@
         <v>64056000</v>
       </c>
       <c r="AI77" t="n">
-        <v>2137280898</v>
+        <v>2115096466</v>
       </c>
       <c r="AJ77" t="n">
         <v>31609434000</v>
@@ -11432,7 +11432,7 @@
         <v>867908929</v>
       </c>
       <c r="AQ77" t="n">
-        <v>632395834</v>
+        <v>632395835</v>
       </c>
       <c r="AR77" t="n">
         <v>1822814124</v>
@@ -11440,7 +11440,7 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr"/>
       <c r="AU77" t="n">
-        <v>6962355250</v>
+        <v>6962355252</v>
       </c>
       <c r="AV77" t="n">
         <v>16750088436</v>
@@ -11457,34 +11457,34 @@
         <v>46173</v>
       </c>
       <c r="B78" t="n">
-        <v>31557335963</v>
+        <v>31529852245</v>
       </c>
       <c r="C78" t="n">
-        <v>24118232383</v>
+        <v>24120363018</v>
       </c>
       <c r="D78" t="n">
-        <v>7439103580</v>
+        <v>7409489227</v>
       </c>
       <c r="E78" t="n">
-        <v>55675568346</v>
+        <v>55650215263</v>
       </c>
       <c r="F78" t="n">
-        <v>63575354725</v>
+        <v>63563467072</v>
       </c>
       <c r="G78" t="n">
-        <v>14126830781</v>
+        <v>14124507396</v>
       </c>
       <c r="H78" t="n">
-        <v>1222605122</v>
+        <v>1222549479</v>
       </c>
       <c r="I78" t="n">
-        <v>30748299</v>
+        <v>30748501</v>
       </c>
       <c r="J78" t="n">
-        <v>25371585804</v>
+        <v>25373660998</v>
       </c>
       <c r="K78" t="n">
-        <v>617450435</v>
+        <v>620395097</v>
       </c>
       <c r="L78" t="n">
         <v>1806544416</v>
@@ -11496,10 +11496,10 @@
         <v>82398</v>
       </c>
       <c r="O78" t="n">
-        <v>912935086</v>
+        <v>912871064</v>
       </c>
       <c r="P78" t="n">
-        <v>155169290</v>
+        <v>155153890</v>
       </c>
       <c r="Q78" t="n">
         <v>305848</v>
@@ -11556,7 +11556,7 @@
         <v>40053800</v>
       </c>
       <c r="AI78" t="n">
-        <v>1683117561</v>
+        <v>1657447109</v>
       </c>
       <c r="AJ78" t="n">
         <v>25568797966</v>
@@ -11580,18 +11580,18 @@
         <v>430988678</v>
       </c>
       <c r="AQ78" t="n">
-        <v>735872995</v>
+        <v>731859065</v>
       </c>
       <c r="AR78" t="n">
-        <v>2058375168</v>
+        <v>2046900168</v>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr"/>
       <c r="AU78" t="n">
-        <v>6290576208</v>
+        <v>6289797046</v>
       </c>
       <c r="AV78" t="n">
-        <v>14825071266</v>
+        <v>14825071267</v>
       </c>
       <c r="AW78" t="n">
         <v>33901960</v>
@@ -11605,34 +11605,34 @@
         <v>46203</v>
       </c>
       <c r="B79" t="n">
-        <v>35492956607</v>
+        <v>35499628278</v>
       </c>
       <c r="C79" t="n">
-        <v>26493857835</v>
+        <v>26495200506</v>
       </c>
       <c r="D79" t="n">
-        <v>8999098772</v>
+        <v>9004427772</v>
       </c>
       <c r="E79" t="n">
-        <v>61986814442</v>
+        <v>61994828784</v>
       </c>
       <c r="F79" t="n">
-        <v>82860091366</v>
+        <v>82859912220</v>
       </c>
       <c r="G79" t="n">
-        <v>14024278044</v>
+        <v>14023235066</v>
       </c>
       <c r="H79" t="n">
-        <v>1322948542</v>
+        <v>1322972352</v>
       </c>
       <c r="I79" t="n">
-        <v>23910838</v>
+        <v>23834159</v>
       </c>
       <c r="J79" t="n">
-        <v>27840717215</v>
+        <v>27842007017</v>
       </c>
       <c r="K79" t="n">
-        <v>938953227</v>
+        <v>950478133</v>
       </c>
       <c r="L79" t="n">
         <v>2770311509</v>
@@ -11644,18 +11644,18 @@
         <v>184747</v>
       </c>
       <c r="O79" t="n">
-        <v>934557701</v>
+        <v>934580723</v>
       </c>
       <c r="P79" t="n">
-        <v>167705205</v>
+        <v>167708805</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="n">
-        <v>1602350318</v>
+        <v>1604689886</v>
       </c>
       <c r="T79" t="n">
-        <v>248837040</v>
+        <v>248809399</v>
       </c>
       <c r="U79" t="n">
         <v>8385042</v>
@@ -11700,7 +11700,7 @@
         <v>89731429</v>
       </c>
       <c r="AI79" t="n">
-        <v>2569324747</v>
+        <v>2561140623</v>
       </c>
       <c r="AJ79" t="n">
         <v>39666979151</v>
@@ -11732,7 +11732,7 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
       <c r="AU79" t="n">
-        <v>6266776914</v>
+        <v>6265912842</v>
       </c>
       <c r="AV79" t="n">
         <v>14505017737</v>
@@ -11749,34 +11749,34 @@
         <v>46234</v>
       </c>
       <c r="B80" t="n">
-        <v>33723397019</v>
+        <v>33577433983</v>
       </c>
       <c r="C80" t="n">
-        <v>27158319765</v>
+        <v>27159421177</v>
       </c>
       <c r="D80" t="n">
-        <v>6565077254</v>
+        <v>6418012806</v>
       </c>
       <c r="E80" t="n">
-        <v>60881716784</v>
+        <v>60736855160</v>
       </c>
       <c r="F80" t="n">
-        <v>77871209960</v>
+        <v>77797817457</v>
       </c>
       <c r="G80" t="n">
-        <v>16655220670</v>
+        <v>16655525507</v>
       </c>
       <c r="H80" t="n">
-        <v>1471041432</v>
+        <v>1471017620</v>
       </c>
       <c r="I80" t="n">
-        <v>26306646</v>
+        <v>26306641</v>
       </c>
       <c r="J80" t="n">
-        <v>28655667843</v>
+        <v>28656745438</v>
       </c>
       <c r="K80" t="n">
-        <v>844057652</v>
+        <v>846757948</v>
       </c>
       <c r="L80" t="n">
         <v>2529930057</v>
@@ -11788,7 +11788,7 @@
         <v>122615</v>
       </c>
       <c r="O80" t="n">
-        <v>813952881</v>
+        <v>814022100</v>
       </c>
       <c r="P80" t="n">
         <v>152934524</v>
@@ -11800,7 +11800,7 @@
         <v>1560</v>
       </c>
       <c r="S80" t="n">
-        <v>1201408088</v>
+        <v>1202269384</v>
       </c>
       <c r="T80" t="n">
         <v>193061335</v>
@@ -11824,10 +11824,10 @@
         <v>904209</v>
       </c>
       <c r="AA80" t="n">
-        <v>589861744</v>
+        <v>547522432</v>
       </c>
       <c r="AB80" t="n">
-        <v>959864111</v>
+        <v>927703584</v>
       </c>
       <c r="AC80" t="n">
         <v>60</v>
@@ -11842,16 +11842,16 @@
         <v>1941216352</v>
       </c>
       <c r="AG80" t="n">
-        <v>28986392</v>
+        <v>28970014</v>
       </c>
       <c r="AH80" t="n">
-        <v>175804570</v>
+        <v>175710260</v>
       </c>
       <c r="AI80" t="n">
-        <v>2131758139</v>
+        <v>2132007782</v>
       </c>
       <c r="AJ80" t="n">
-        <v>35002833875</v>
+        <v>34974584205</v>
       </c>
       <c r="AK80" t="n">
         <v>1798</v>
@@ -11860,16 +11860,16 @@
         <v>1000</v>
       </c>
       <c r="AM80" t="n">
-        <v>4737463030</v>
+        <v>4629365093</v>
       </c>
       <c r="AN80" t="n">
-        <v>7674971451</v>
+        <v>7672032952</v>
       </c>
       <c r="AO80" t="n">
-        <v>736291615</v>
+        <v>737457317</v>
       </c>
       <c r="AP80" t="n">
-        <v>1020215096</v>
+        <v>1020333259</v>
       </c>
       <c r="AQ80" t="n">
         <v>647927068</v>
@@ -11880,16 +11880,16 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr"/>
       <c r="AU80" t="n">
-        <v>5869552552</v>
+        <v>5870448703</v>
       </c>
       <c r="AV80" t="n">
         <v>13405907808</v>
       </c>
       <c r="AW80" t="n">
-        <v>24415856</v>
+        <v>23848605</v>
       </c>
       <c r="AX80" t="n">
-        <v>62866000</v>
+        <v>61696410</v>
       </c>
     </row>
     <row r="81">
@@ -11897,37 +11897,37 @@
         <v>46265</v>
       </c>
       <c r="B81" t="n">
-        <v>33157804370</v>
+        <v>32732183002</v>
       </c>
       <c r="C81" t="n">
-        <v>25763862100</v>
+        <v>25823660146</v>
       </c>
       <c r="D81" t="n">
-        <v>7393942270</v>
+        <v>6908522856</v>
       </c>
       <c r="E81" t="n">
-        <v>58921666470</v>
+        <v>58555843148</v>
       </c>
       <c r="F81" t="n">
-        <v>77119199389</v>
+        <v>76672534789</v>
       </c>
       <c r="G81" t="n">
-        <v>14073182023</v>
+        <v>14050480944</v>
       </c>
       <c r="H81" t="n">
-        <v>1548184686</v>
+        <v>1546788681</v>
       </c>
       <c r="I81" t="n">
-        <v>19241881</v>
+        <v>19260288</v>
       </c>
       <c r="J81" t="n">
-        <v>27331288667</v>
+        <v>27389709115</v>
       </c>
       <c r="K81" t="n">
-        <v>753147930</v>
+        <v>752297715</v>
       </c>
       <c r="L81" t="n">
-        <v>2221291720</v>
+        <v>2220715368</v>
       </c>
       <c r="M81" t="n">
         <v>170442</v>
@@ -11936,7 +11936,7 @@
         <v>143344</v>
       </c>
       <c r="O81" t="n">
-        <v>1094109253</v>
+        <v>1094443369</v>
       </c>
       <c r="P81" t="n">
         <v>206264157</v>
@@ -11944,7 +11944,7 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="n">
-        <v>967242706</v>
+        <v>967264803</v>
       </c>
       <c r="T81" t="n">
         <v>162300453</v>
@@ -11968,30 +11968,30 @@
         <v>1452782</v>
       </c>
       <c r="AA81" t="n">
-        <v>893582419</v>
+        <v>852206570</v>
       </c>
       <c r="AB81" t="n">
-        <v>1438094595</v>
+        <v>1383886863</v>
       </c>
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="n">
-        <v>1002656682</v>
+        <v>989881482</v>
       </c>
       <c r="AF81" t="n">
-        <v>4653100189</v>
+        <v>4648770261</v>
       </c>
       <c r="AG81" t="n">
-        <v>33273820</v>
+        <v>33267163</v>
       </c>
       <c r="AH81" t="n">
-        <v>199281400</v>
+        <v>199242360</v>
       </c>
       <c r="AI81" t="n">
-        <v>2051566400</v>
+        <v>2037904434</v>
       </c>
       <c r="AJ81" t="n">
-        <v>34406447895</v>
+        <v>34351503645</v>
       </c>
       <c r="AK81" t="n">
         <v>6950029</v>
@@ -12000,22 +12000,22 @@
         <v>78331372</v>
       </c>
       <c r="AM81" t="n">
-        <v>4828191084</v>
+        <v>4588224684</v>
       </c>
       <c r="AN81" t="n">
-        <v>8379911835</v>
+        <v>8358755854</v>
       </c>
       <c r="AO81" t="n">
-        <v>547298813</v>
+        <v>561128509</v>
       </c>
       <c r="AP81" t="n">
-        <v>797225701</v>
+        <v>798168982</v>
       </c>
       <c r="AQ81" t="n">
-        <v>646488066</v>
+        <v>644929294</v>
       </c>
       <c r="AR81" t="n">
-        <v>1790486389</v>
+        <v>1785896563</v>
       </c>
       <c r="AS81" t="n">
         <v>360</v>
@@ -12024,16 +12024,156 @@
         <v>0</v>
       </c>
       <c r="AU81" t="n">
-        <v>4410039153</v>
+        <v>4414965758</v>
       </c>
       <c r="AV81" t="n">
-        <v>9808807495</v>
+        <v>9810807500</v>
       </c>
       <c r="AW81" t="n">
         <v>44621019</v>
       </c>
       <c r="AX81" t="n">
         <v>109088024</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>34418070076</v>
+      </c>
+      <c r="C82" t="n">
+        <v>26677510096</v>
+      </c>
+      <c r="D82" t="n">
+        <v>7740559980</v>
+      </c>
+      <c r="E82" t="n">
+        <v>61095580172</v>
+      </c>
+      <c r="F82" t="n">
+        <v>76342513744</v>
+      </c>
+      <c r="G82" t="n">
+        <v>14665789542</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1611232587</v>
+      </c>
+      <c r="I82" t="n">
+        <v>27463449</v>
+      </c>
+      <c r="J82" t="n">
+        <v>28316206132</v>
+      </c>
+      <c r="K82" t="n">
+        <v>809708916</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2306235692</v>
+      </c>
+      <c r="M82" t="n">
+        <v>144681</v>
+      </c>
+      <c r="N82" t="n">
+        <v>122543</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1292800592</v>
+      </c>
+      <c r="P82" t="n">
+        <v>235659946</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>950751177</v>
+      </c>
+      <c r="T82" t="n">
+        <v>156467198</v>
+      </c>
+      <c r="U82" t="n">
+        <v>10523613</v>
+      </c>
+      <c r="V82" t="n">
+        <v>988603</v>
+      </c>
+      <c r="W82" t="n">
+        <v>892280162</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1801287673</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1255725</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1333748</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>649437972</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>942054629</v>
+      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="n">
+        <v>1228786726</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>5207728793</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>37058160</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>220704294</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1771842975</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>31660490297</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>5139747</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>61011592</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>6498868606</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>11689652591</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>631617247</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>893774707</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>755950210</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1941525390</v>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="n">
+        <v>3473089697</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>117130000</v>
       </c>
     </row>
   </sheetData>
